--- a/VerveStacks_BIH_grids_kan10/Sets-vervestacks.xlsx
+++ b/VerveStacks_BIH_grids_kan10/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BIH_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{61A383A6-1697-428A-BEF7-EE78143A4268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A2A58480-A68A-4216-808E-892293C57845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="181">
   <si>
     <t>~TFM_Psets</t>
   </si>
@@ -379,12 +379,6 @@
     <t>*[_]Mostar_BIH</t>
   </si>
   <si>
-    <t>p_Vogosca_BIH</t>
-  </si>
-  <si>
-    <t>*[_]Vogosca_BIH</t>
-  </si>
-  <si>
     <t>p_Bijeljina_BIH</t>
   </si>
   <si>
@@ -397,6 +391,12 @@
     <t>*[_]Trebinje_BIH</t>
   </si>
   <si>
+    <t>p_Travnik_BIH</t>
+  </si>
+  <si>
+    <t>*[_]Travnik_BIH</t>
+  </si>
+  <si>
     <t>p_Doboj_BIH</t>
   </si>
   <si>
@@ -415,16 +415,22 @@
     <t>*[_]Bratunac_BIH</t>
   </si>
   <si>
-    <t>p_Zenica_BIH</t>
-  </si>
-  <si>
-    <t>*[_]Zenica_BIH</t>
-  </si>
-  <si>
     <t>p_SirokiBrijeg_BIH</t>
   </si>
   <si>
     <t>*[_]SirokiBrijeg_BIH</t>
+  </si>
+  <si>
+    <t>p_Orasje_BIH</t>
+  </si>
+  <si>
+    <t>*[_]Orasje_BIH</t>
+  </si>
+  <si>
+    <t>p_Sarajevo_BIH</t>
+  </si>
+  <si>
+    <t>*[_]Sarajevo_BIH</t>
   </si>
   <si>
     <t>s_ogci11364_BIH</t>
@@ -1419,8 +1425,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22314482-E318-441F-BA84-2274E799258E}">
-  <dimension ref="B9:E45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C359423F-8298-4085-84D6-27EE627FCCFF}">
+  <dimension ref="B9:E46"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="9" spans="2:5" x14ac:dyDescent="0.45">
@@ -1929,6 +1935,20 @@
         <v>178</v>
       </c>
       <c r="E45" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B46" t="s">
+        <v>179</v>
+      </c>
+      <c r="C46" t="s">
+        <v>180</v>
+      </c>
+      <c r="D46" t="s">
+        <v>180</v>
+      </c>
+      <c r="E46" t="s">
         <v>110</v>
       </c>
     </row>
